--- a/01. Preprocessing data/data_CSV/04_ABUS.xlsx
+++ b/01. Preprocessing data/data_CSV/04_ABUS.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$N$599</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1363">
   <si>
     <t>Name</t>
   </si>
@@ -4065,12 +4068,6 @@
     <t>2 5</t>
   </si>
   <si>
-    <t>ABUS</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
     <t>ABUS_nodle_size</t>
   </si>
   <si>
@@ -4111,6 +4108,9 @@
   </si>
   <si>
     <t>ABUS_calcinates</t>
+  </si>
+  <si>
+    <t>ABUS_skin</t>
   </si>
 </sst>
 </file>
@@ -4769,6 +4769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N599"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4789,37 +4790,37 @@
         <v>3</v>
       </c>
       <c r="E1" s="33" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F1" s="33" t="s">
         <v>1348</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="G1" s="33" t="s">
+        <v>1349</v>
+      </c>
+      <c r="H1" s="33" t="s">
         <v>1350</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="I1" s="33" t="s">
         <v>1351</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>1352</v>
-      </c>
-      <c r="I1" s="33" t="s">
+      <c r="J1" s="33" t="s">
         <v>1353</v>
       </c>
-      <c r="J1" s="33" t="s">
-        <v>1355</v>
-      </c>
       <c r="K1" s="45" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="L1" s="46" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M1" s="46" t="s">
+        <v>1360</v>
+      </c>
+      <c r="N1" s="46" t="s">
         <v>1361</v>
       </c>
-      <c r="M1" s="46" t="s">
-        <v>1362</v>
-      </c>
-      <c r="N1" s="46" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -4922,7 +4923,7 @@
       </c>
       <c r="G4" s="34"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -4966,7 +4967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -4988,7 +4989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -5032,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -5050,7 +5051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
@@ -5135,7 +5136,7 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
@@ -5179,7 +5180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>32</v>
       </c>
@@ -5220,7 +5221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
@@ -5242,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
@@ -5264,7 +5265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
@@ -5308,7 +5309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
@@ -5330,7 +5331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -5374,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -5418,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>52</v>
       </c>
@@ -5462,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>54</v>
       </c>
@@ -5506,7 +5507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>57</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>60</v>
       </c>
@@ -5556,7 +5557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>63</v>
       </c>
@@ -5588,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="L24" s="31">
         <v>3</v>
@@ -5600,7 +5601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>66</v>
       </c>
@@ -5619,7 +5620,7 @@
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -5663,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>71</v>
       </c>
@@ -5682,7 +5683,7 @@
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>73</v>
       </c>
@@ -5726,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
@@ -5745,7 +5746,7 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>78</v>
       </c>
@@ -5767,7 +5768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>80</v>
       </c>
@@ -5786,7 +5787,7 @@
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>83</v>
       </c>
@@ -5874,7 +5875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>87</v>
       </c>
@@ -5918,7 +5919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -5940,7 +5941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>93</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>96</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>99</v>
       </c>
@@ -6054,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
@@ -6079,7 +6080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>103</v>
       </c>
@@ -6123,7 +6124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>105</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>108</v>
       </c>
@@ -6189,7 +6190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>111</v>
       </c>
@@ -6211,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
         <v>113</v>
       </c>
@@ -6255,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>116</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>119</v>
       </c>
@@ -6343,7 +6344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>121</v>
       </c>
@@ -6362,7 +6363,7 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>123</v>
       </c>
@@ -6381,7 +6382,7 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>125</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>127</v>
       </c>
@@ -6444,7 +6445,7 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>129</v>
       </c>
@@ -6488,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>131</v>
       </c>
@@ -6532,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>134</v>
       </c>
@@ -6551,7 +6552,7 @@
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>136</v>
       </c>
@@ -6595,7 +6596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>138</v>
       </c>
@@ -6614,7 +6615,7 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>140</v>
       </c>
@@ -6658,7 +6659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>142</v>
       </c>
@@ -6677,7 +6678,7 @@
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>145</v>
       </c>
@@ -6721,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>148</v>
       </c>
@@ -6740,7 +6741,7 @@
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
         <v>151</v>
       </c>
@@ -6784,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
         <v>154</v>
       </c>
@@ -6803,7 +6804,7 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>156</v>
       </c>
@@ -6847,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>158</v>
       </c>
@@ -6891,7 +6892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>160</v>
       </c>
@@ -6910,7 +6911,7 @@
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>163</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>165</v>
       </c>
@@ -6973,7 +6974,7 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20" t="s">
         <v>167</v>
       </c>
@@ -6992,7 +6993,7 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>169</v>
       </c>
@@ -7036,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>171</v>
       </c>
@@ -7055,7 +7056,7 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>174</v>
       </c>
@@ -7087,7 +7088,7 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -7099,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>176</v>
       </c>
@@ -7143,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>178</v>
       </c>
@@ -7162,7 +7163,7 @@
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>180</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>182</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>184</v>
       </c>
@@ -7247,7 +7248,7 @@
       <c r="H75" s="13"/>
       <c r="I75" s="13"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>186</v>
       </c>
@@ -7291,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>188</v>
       </c>
@@ -7310,7 +7311,7 @@
       <c r="H77" s="13"/>
       <c r="I77" s="13"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>190</v>
       </c>
@@ -7354,7 +7355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>192</v>
       </c>
@@ -7398,7 +7399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>195</v>
       </c>
@@ -7417,7 +7418,7 @@
       <c r="H80" s="13"/>
       <c r="I80" s="13"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>197</v>
       </c>
@@ -7436,7 +7437,7 @@
       <c r="H81" s="13"/>
       <c r="I81" s="13"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>199</v>
       </c>
@@ -7480,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>201</v>
       </c>
@@ -7499,7 +7500,7 @@
       <c r="H83" s="13"/>
       <c r="I83" s="13"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>203</v>
       </c>
@@ -7543,7 +7544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>206</v>
       </c>
@@ -7562,7 +7563,7 @@
       <c r="H85" s="13"/>
       <c r="I85" s="13"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
         <v>209</v>
       </c>
@@ -7581,7 +7582,7 @@
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="16" t="s">
         <v>211</v>
       </c>
@@ -7600,7 +7601,7 @@
       <c r="H87" s="13"/>
       <c r="I87" s="13"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="21" t="s">
         <v>213</v>
       </c>
@@ -7644,7 +7645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>215</v>
       </c>
@@ -7688,7 +7689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>218</v>
       </c>
@@ -7732,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>220</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>222</v>
       </c>
@@ -7795,7 +7796,7 @@
       <c r="H92" s="13"/>
       <c r="I92" s="13"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>224</v>
       </c>
@@ -7814,7 +7815,7 @@
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>226</v>
       </c>
@@ -7858,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>228</v>
       </c>
@@ -7877,7 +7878,7 @@
       <c r="H95" s="13"/>
       <c r="I95" s="13"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>230</v>
       </c>
@@ -7896,7 +7897,7 @@
       <c r="H96" s="13"/>
       <c r="I96" s="13"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>233</v>
       </c>
@@ -7940,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>235</v>
       </c>
@@ -7968,7 +7969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>238</v>
       </c>
@@ -8012,7 +8013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -8031,7 +8032,7 @@
       <c r="H100" s="13"/>
       <c r="I100" s="13"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -8050,7 +8051,7 @@
       <c r="H101" s="13"/>
       <c r="I101" s="13"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>244</v>
       </c>
@@ -8094,7 +8095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>246</v>
       </c>
@@ -8113,7 +8114,7 @@
       <c r="H103" s="13"/>
       <c r="I103" s="13"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>248</v>
       </c>
@@ -8157,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>250</v>
       </c>
@@ -8179,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>252</v>
       </c>
@@ -8223,7 +8224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>255</v>
       </c>
@@ -8267,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>257</v>
       </c>
@@ -8296,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>260</v>
       </c>
@@ -8315,7 +8316,7 @@
       <c r="H109" s="13"/>
       <c r="I109" s="13"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>262</v>
       </c>
@@ -8359,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>264</v>
       </c>
@@ -8387,7 +8388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>266</v>
       </c>
@@ -8431,7 +8432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>268</v>
       </c>
@@ -8475,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>271</v>
       </c>
@@ -8494,7 +8495,7 @@
       <c r="H114" s="13"/>
       <c r="I114" s="13"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>273</v>
       </c>
@@ -8538,7 +8539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>276</v>
       </c>
@@ -8557,7 +8558,7 @@
       <c r="H116" s="13"/>
       <c r="I116" s="13"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>279</v>
       </c>
@@ -8601,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>282</v>
       </c>
@@ -8620,7 +8621,7 @@
       <c r="H118" s="13"/>
       <c r="I118" s="13"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>284</v>
       </c>
@@ -8664,7 +8665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
         <v>286</v>
       </c>
@@ -8683,7 +8684,7 @@
       <c r="H120" s="13"/>
       <c r="I120" s="13"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>288</v>
       </c>
@@ -8705,7 +8706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
         <v>290</v>
       </c>
@@ -8724,7 +8725,7 @@
       <c r="H122" s="13"/>
       <c r="I122" s="13"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>292</v>
       </c>
@@ -8768,7 +8769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>294</v>
       </c>
@@ -8812,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>296</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>299</v>
       </c>
@@ -8878,7 +8879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>301</v>
       </c>
@@ -8897,7 +8898,7 @@
       <c r="H127" s="13"/>
       <c r="I127" s="13"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>303</v>
       </c>
@@ -8941,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="13" t="s">
         <v>305</v>
       </c>
@@ -8985,7 +8986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
         <v>307</v>
       </c>
@@ -9004,7 +9005,7 @@
       <c r="H130" s="13"/>
       <c r="I130" s="13"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="13" t="s">
         <v>309</v>
       </c>
@@ -9023,7 +9024,7 @@
       <c r="H131" s="13"/>
       <c r="I131" s="13"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -9055,7 +9056,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="L132">
         <v>3</v>
@@ -9067,7 +9068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="13" t="s">
         <v>313</v>
       </c>
@@ -9111,7 +9112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="13" t="s">
         <v>315</v>
       </c>
@@ -9133,7 +9134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
         <v>317</v>
       </c>
@@ -9177,7 +9178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="13" t="s">
         <v>319</v>
       </c>
@@ -9202,7 +9203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
         <v>321</v>
       </c>
@@ -9278,7 +9279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="13" t="s">
         <v>327</v>
       </c>
@@ -9322,7 +9323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="13" t="s">
         <v>329</v>
       </c>
@@ -9341,7 +9342,7 @@
       <c r="H140" s="13"/>
       <c r="I140" s="13"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="13" t="s">
         <v>332</v>
       </c>
@@ -9385,7 +9386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="13" t="s">
         <v>335</v>
       </c>
@@ -9407,7 +9408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>338</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="13" t="s">
         <v>340</v>
       </c>
@@ -9470,7 +9471,7 @@
       <c r="H144" s="13"/>
       <c r="I144" s="13"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>342</v>
       </c>
@@ -9514,7 +9515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>344</v>
       </c>
@@ -9533,7 +9534,7 @@
       <c r="H146" s="13"/>
       <c r="I146" s="13"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>346</v>
       </c>
@@ -9577,7 +9578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="13" t="s">
         <v>348</v>
       </c>
@@ -9609,7 +9610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="s">
         <v>351</v>
       </c>
@@ -9628,7 +9629,7 @@
       <c r="H149" s="13"/>
       <c r="I149" s="13"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="s">
         <v>353</v>
       </c>
@@ -9672,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
         <v>355</v>
       </c>
@@ -9691,7 +9692,7 @@
       <c r="H151" s="13"/>
       <c r="I151" s="13"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="13" t="s">
         <v>357</v>
       </c>
@@ -9710,7 +9711,7 @@
       <c r="H152" s="13"/>
       <c r="I152" s="13"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="13" t="s">
         <v>359</v>
       </c>
@@ -9754,7 +9755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>361</v>
       </c>
@@ -9798,7 +9799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>363</v>
       </c>
@@ -9817,7 +9818,7 @@
       <c r="H155" s="13"/>
       <c r="I155" s="13"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>365</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>367</v>
       </c>
@@ -9877,7 +9878,7 @@
       <c r="H157" s="13"/>
       <c r="I157" s="13"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>369</v>
       </c>
@@ -9921,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>371</v>
       </c>
@@ -9940,7 +9941,7 @@
       <c r="H159" s="13"/>
       <c r="I159" s="13"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="13" t="s">
         <v>373</v>
       </c>
@@ -9959,7 +9960,7 @@
       <c r="H160" s="13"/>
       <c r="I160" s="13"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="13" t="s">
         <v>376</v>
       </c>
@@ -10003,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="13" t="s">
         <v>378</v>
       </c>
@@ -10047,7 +10048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="13" t="s">
         <v>380</v>
       </c>
@@ -10066,7 +10067,7 @@
       <c r="H163" s="13"/>
       <c r="I163" s="13"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="16" t="s">
         <v>382</v>
       </c>
@@ -10154,7 +10155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="13" t="s">
         <v>386</v>
       </c>
@@ -10173,7 +10174,7 @@
       <c r="H166" s="13"/>
       <c r="I166" s="13"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>388</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="13" t="s">
         <v>391</v>
       </c>
@@ -10242,7 +10243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="13" t="s">
         <v>393</v>
       </c>
@@ -10286,7 +10287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="13" t="s">
         <v>395</v>
       </c>
@@ -10305,7 +10306,7 @@
       <c r="H170" s="13"/>
       <c r="I170" s="13"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="13" t="s">
         <v>397</v>
       </c>
@@ -10324,7 +10325,7 @@
       <c r="H171" s="13"/>
       <c r="I171" s="13"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="13" t="s">
         <v>399</v>
       </c>
@@ -10368,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="13" t="s">
         <v>401</v>
       </c>
@@ -10412,7 +10413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="13" t="s">
         <v>403</v>
       </c>
@@ -10431,7 +10432,7 @@
       <c r="H174" s="13"/>
       <c r="I174" s="13"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="13" t="s">
         <v>405</v>
       </c>
@@ -10472,7 +10473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="13" t="s">
         <v>407</v>
       </c>
@@ -10491,7 +10492,7 @@
       <c r="H176" s="13"/>
       <c r="I176" s="13"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>409</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="13" t="s">
         <v>411</v>
       </c>
@@ -10557,7 +10558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="13" t="s">
         <v>413</v>
       </c>
@@ -10576,7 +10577,7 @@
       <c r="H179" s="13"/>
       <c r="I179" s="13"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="13" t="s">
         <v>415</v>
       </c>
@@ -10620,7 +10621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="13" t="s">
         <v>418</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="13" t="s">
         <v>421</v>
       </c>
@@ -10683,7 +10684,7 @@
       <c r="H182" s="13"/>
       <c r="I182" s="13"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="13" t="s">
         <v>423</v>
       </c>
@@ -10727,7 +10728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="13" t="s">
         <v>425</v>
       </c>
@@ -10746,7 +10747,7 @@
       <c r="H184" s="13"/>
       <c r="I184" s="13"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="13" t="s">
         <v>427</v>
       </c>
@@ -10790,7 +10791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="13" t="s">
         <v>429</v>
       </c>
@@ -10809,7 +10810,7 @@
       <c r="H186" s="13"/>
       <c r="I186" s="13"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="13" t="s">
         <v>431</v>
       </c>
@@ -10853,7 +10854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
         <v>433</v>
       </c>
@@ -10872,7 +10873,7 @@
       <c r="H188" s="13"/>
       <c r="I188" s="13"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="13" t="s">
         <v>435</v>
       </c>
@@ -10916,7 +10917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="13" t="s">
         <v>437</v>
       </c>
@@ -10935,7 +10936,7 @@
       <c r="H190" s="13"/>
       <c r="I190" s="13"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="13" t="s">
         <v>439</v>
       </c>
@@ -10957,7 +10958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="13" t="s">
         <v>441</v>
       </c>
@@ -11001,7 +11002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="13" t="s">
         <v>443</v>
       </c>
@@ -11064,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="13" t="s">
         <v>447</v>
       </c>
@@ -11108,7 +11109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="24" t="s">
         <v>449</v>
       </c>
@@ -11127,7 +11128,7 @@
       <c r="H196" s="13"/>
       <c r="I196" s="13"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="13" t="s">
         <v>451</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>453</v>
       </c>
@@ -11190,7 +11191,7 @@
       <c r="H198" s="13"/>
       <c r="I198" s="13"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
         <v>455</v>
       </c>
@@ -11234,7 +11235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="13" t="s">
         <v>458</v>
       </c>
@@ -11278,7 +11279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
         <v>460</v>
       </c>
@@ -11297,7 +11298,7 @@
       <c r="H201" s="13"/>
       <c r="I201" s="13"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="13" t="s">
         <v>462</v>
       </c>
@@ -11373,7 +11374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="13" t="s">
         <v>467</v>
       </c>
@@ -11417,7 +11418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>469</v>
       </c>
@@ -11461,7 +11462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="13" t="s">
         <v>472</v>
       </c>
@@ -11480,7 +11481,7 @@
       <c r="H206" s="13"/>
       <c r="I206" s="13"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="13" t="s">
         <v>474</v>
       </c>
@@ -11559,7 +11560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="13" t="s">
         <v>478</v>
       </c>
@@ -11603,7 +11604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="13" t="s">
         <v>480</v>
       </c>
@@ -11622,7 +11623,7 @@
       <c r="H210" s="13"/>
       <c r="I210" s="13"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="13" t="s">
         <v>482</v>
       </c>
@@ -11641,7 +11642,7 @@
       <c r="H211" s="13"/>
       <c r="I211" s="13"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="13" t="s">
         <v>484</v>
       </c>
@@ -11685,7 +11686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
         <v>486</v>
       </c>
@@ -11704,7 +11705,7 @@
       <c r="H213" s="13"/>
       <c r="I213" s="13"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="13" t="s">
         <v>488</v>
       </c>
@@ -11723,7 +11724,7 @@
       <c r="H214" s="13"/>
       <c r="I214" s="13"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="16" t="s">
         <v>490</v>
       </c>
@@ -11767,7 +11768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="13" t="s">
         <v>492</v>
       </c>
@@ -11811,7 +11812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="13" t="s">
         <v>495</v>
       </c>
@@ -11830,7 +11831,7 @@
       <c r="H217" s="13"/>
       <c r="I217" s="13"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="13" t="s">
         <v>497</v>
       </c>
@@ -11874,7 +11875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="13" t="s">
         <v>499</v>
       </c>
@@ -11893,7 +11894,7 @@
       <c r="H219" s="13"/>
       <c r="I219" s="13"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="13" t="s">
         <v>501</v>
       </c>
@@ -11937,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="13" t="s">
         <v>503</v>
       </c>
@@ -11956,7 +11957,7 @@
       <c r="H221" s="13"/>
       <c r="I221" s="13"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="13" t="s">
         <v>505</v>
       </c>
@@ -11975,7 +11976,7 @@
       <c r="H222" s="13"/>
       <c r="I222" s="13"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="13" t="s">
         <v>507</v>
       </c>
@@ -12019,7 +12020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="13" t="s">
         <v>509</v>
       </c>
@@ -12038,7 +12039,7 @@
       <c r="H224" s="13"/>
       <c r="I224" s="13"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="13" t="s">
         <v>511</v>
       </c>
@@ -12082,7 +12083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="13" t="s">
         <v>513</v>
       </c>
@@ -12101,7 +12102,7 @@
       <c r="H226" s="13"/>
       <c r="I226" s="13"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="13" t="s">
         <v>515</v>
       </c>
@@ -12145,7 +12146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="13" t="s">
         <v>517</v>
       </c>
@@ -12164,7 +12165,7 @@
       <c r="H228" s="13"/>
       <c r="I228" s="13"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="13" t="s">
         <v>519</v>
       </c>
@@ -12183,7 +12184,7 @@
       <c r="H229" s="13"/>
       <c r="I229" s="13"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="16" t="s">
         <v>522</v>
       </c>
@@ -12227,7 +12228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="13" t="s">
         <v>525</v>
       </c>
@@ -12271,7 +12272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="13" t="s">
         <v>527</v>
       </c>
@@ -12315,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="13" t="s">
         <v>529</v>
       </c>
@@ -12334,7 +12335,7 @@
       <c r="H233" s="13"/>
       <c r="I233" s="13"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="13" t="s">
         <v>531</v>
       </c>
@@ -12353,7 +12354,7 @@
       <c r="H234" s="13"/>
       <c r="I234" s="13"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="13" t="s">
         <v>533</v>
       </c>
@@ -12394,7 +12395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
         <v>535</v>
       </c>
@@ -12413,7 +12414,7 @@
       <c r="H236" s="13"/>
       <c r="I236" s="13"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="13" t="s">
         <v>537</v>
       </c>
@@ -12454,7 +12455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>539</v>
       </c>
@@ -12476,7 +12477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="13" t="s">
         <v>541</v>
       </c>
@@ -12520,7 +12521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="13" t="s">
         <v>543</v>
       </c>
@@ -12539,7 +12540,7 @@
       <c r="H240" s="13"/>
       <c r="I240" s="13"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>545</v>
       </c>
@@ -12565,7 +12566,7 @@
         <v>2</v>
       </c>
       <c r="I241" s="13" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J241" s="13">
         <v>1</v>
@@ -12583,7 +12584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="13" t="s">
         <v>547</v>
       </c>
@@ -12611,7 +12612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="13" t="s">
         <v>549</v>
       </c>
@@ -12655,7 +12656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="13" t="s">
         <v>551</v>
       </c>
@@ -12668,15 +12669,13 @@
       <c r="D244" s="13">
         <v>2</v>
       </c>
-      <c r="E244" s="13" t="s">
-        <v>1349</v>
-      </c>
+      <c r="E244" s="13"/>
       <c r="F244" s="13"/>
       <c r="G244" s="41"/>
       <c r="H244" s="13"/>
       <c r="I244" s="13"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="13" t="s">
         <v>553</v>
       </c>
@@ -12695,7 +12694,7 @@
       <c r="H245" s="13"/>
       <c r="I245" s="13"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="13" t="s">
         <v>555</v>
       </c>
@@ -12739,7 +12738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="13" t="s">
         <v>558</v>
       </c>
@@ -12761,7 +12760,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="13" t="s">
         <v>560</v>
       </c>
@@ -12805,7 +12804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="13" t="s">
         <v>563</v>
       </c>
@@ -12849,7 +12848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="13" t="s">
         <v>566</v>
       </c>
@@ -12868,7 +12867,7 @@
       <c r="H250" s="13"/>
       <c r="I250" s="13"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="25" t="s">
         <v>569</v>
       </c>
@@ -12912,7 +12911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="25" t="s">
         <v>572</v>
       </c>
@@ -12956,7 +12955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="13" t="s">
         <v>575</v>
       </c>
@@ -13000,7 +12999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="13" t="s">
         <v>577</v>
       </c>
@@ -13019,7 +13018,7 @@
       <c r="H254" s="13"/>
       <c r="I254" s="13"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="13" t="s">
         <v>579</v>
       </c>
@@ -13063,7 +13062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="13" t="s">
         <v>581</v>
       </c>
@@ -13082,7 +13081,7 @@
       <c r="H256" s="13"/>
       <c r="I256" s="13"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="13" t="s">
         <v>583</v>
       </c>
@@ -13126,7 +13125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="13" t="s">
         <v>585</v>
       </c>
@@ -13145,7 +13144,7 @@
       <c r="H258" s="13"/>
       <c r="I258" s="13"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="13" t="s">
         <v>587</v>
       </c>
@@ -13189,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="13" t="s">
         <v>589</v>
       </c>
@@ -13208,7 +13207,7 @@
       <c r="H260" s="13"/>
       <c r="I260" s="13"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="7" t="s">
         <v>591</v>
       </c>
@@ -13252,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="13" t="s">
         <v>593</v>
       </c>
@@ -13271,7 +13270,7 @@
       <c r="H262" s="13"/>
       <c r="I262" s="13"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="13" t="s">
         <v>595</v>
       </c>
@@ -13315,7 +13314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="13" t="s">
         <v>597</v>
       </c>
@@ -13337,7 +13336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="13" t="s">
         <v>599</v>
       </c>
@@ -13381,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="13" t="s">
         <v>601</v>
       </c>
@@ -13400,7 +13399,7 @@
       <c r="H266" s="13"/>
       <c r="I266" s="13"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="13" t="s">
         <v>604</v>
       </c>
@@ -13444,7 +13443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="13" t="s">
         <v>606</v>
       </c>
@@ -13463,7 +13462,7 @@
       <c r="H268" s="13"/>
       <c r="I268" s="13"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="13" t="s">
         <v>608</v>
       </c>
@@ -13498,7 +13497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="13" t="s">
         <v>610</v>
       </c>
@@ -13517,7 +13516,7 @@
       <c r="H270" s="13"/>
       <c r="I270" s="13"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="25" t="s">
         <v>612</v>
       </c>
@@ -13561,7 +13560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="13" t="s">
         <v>614</v>
       </c>
@@ -13605,7 +13604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="13" t="s">
         <v>616</v>
       </c>
@@ -13627,7 +13626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="13" t="s">
         <v>618</v>
       </c>
@@ -13646,7 +13645,7 @@
       <c r="H274" s="13"/>
       <c r="I274" s="13"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="25" t="s">
         <v>620</v>
       </c>
@@ -13678,7 +13677,7 @@
         <v>2</v>
       </c>
       <c r="K275" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="L275">
         <v>2</v>
@@ -13690,7 +13689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="13" t="s">
         <v>623</v>
       </c>
@@ -13734,7 +13733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="13" t="s">
         <v>625</v>
       </c>
@@ -13753,7 +13752,7 @@
       <c r="H277" s="13"/>
       <c r="I277" s="13"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="13" t="s">
         <v>628</v>
       </c>
@@ -13797,7 +13796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="13" t="s">
         <v>630</v>
       </c>
@@ -13819,7 +13818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="13" t="s">
         <v>632</v>
       </c>
@@ -13838,7 +13837,7 @@
       <c r="H280" s="13"/>
       <c r="I280" s="13"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="13" t="s">
         <v>634</v>
       </c>
@@ -13857,7 +13856,7 @@
       <c r="H281" s="13"/>
       <c r="I281" s="13"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="13" t="s">
         <v>636</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="13" t="s">
         <v>638</v>
       </c>
@@ -13923,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="13" t="s">
         <v>640</v>
       </c>
@@ -13967,7 +13966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="13" t="s">
         <v>642</v>
       </c>
@@ -13986,7 +13985,7 @@
       <c r="H285" s="13"/>
       <c r="I285" s="13"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="13" t="s">
         <v>644</v>
       </c>
@@ -14030,7 +14029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="25" t="s">
         <v>646</v>
       </c>
@@ -14074,7 +14073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="13" t="s">
         <v>648</v>
       </c>
@@ -14106,7 +14105,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="13" t="s">
         <v>651</v>
       </c>
@@ -14150,7 +14149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="13" t="s">
         <v>653</v>
       </c>
@@ -14169,7 +14168,7 @@
       <c r="H290" s="13"/>
       <c r="I290" s="13"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="13" t="s">
         <v>655</v>
       </c>
@@ -14188,7 +14187,7 @@
       <c r="H291" s="13"/>
       <c r="I291" s="13"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="13" t="s">
         <v>657</v>
       </c>
@@ -14232,7 +14231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="13" t="s">
         <v>660</v>
       </c>
@@ -14251,7 +14250,7 @@
       <c r="H293" s="13"/>
       <c r="I293" s="13"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="13" t="s">
         <v>662</v>
       </c>
@@ -14295,7 +14294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="13" t="s">
         <v>664</v>
       </c>
@@ -14314,7 +14313,7 @@
       <c r="H295" s="13"/>
       <c r="I295" s="13"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="13" t="s">
         <v>666</v>
       </c>
@@ -14358,7 +14357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="13" t="s">
         <v>668</v>
       </c>
@@ -14377,7 +14376,7 @@
       <c r="H297" s="13"/>
       <c r="I297" s="13"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="13" t="s">
         <v>671</v>
       </c>
@@ -14421,7 +14420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="13" t="s">
         <v>673</v>
       </c>
@@ -14442,7 +14441,7 @@
       <c r="H299" s="13"/>
       <c r="I299" s="13"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="13" t="s">
         <v>676</v>
       </c>
@@ -14463,7 +14462,7 @@
       <c r="H300" s="13"/>
       <c r="I300" s="13"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="13" t="s">
         <v>678</v>
       </c>
@@ -14528,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="13" t="s">
         <v>683</v>
       </c>
@@ -14572,7 +14571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="13" t="s">
         <v>685</v>
       </c>
@@ -14593,7 +14592,7 @@
       <c r="H304" s="13"/>
       <c r="I304" s="13"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="13" t="s">
         <v>687</v>
       </c>
@@ -14634,7 +14633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="13" t="s">
         <v>689</v>
       </c>
@@ -14675,7 +14674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="13" t="s">
         <v>691</v>
       </c>
@@ -14696,7 +14695,7 @@
       <c r="H307" s="13"/>
       <c r="I307" s="13"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="13" t="s">
         <v>693</v>
       </c>
@@ -14717,7 +14716,7 @@
       <c r="H308" s="13"/>
       <c r="I308" s="13"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>695</v>
       </c>
@@ -14736,7 +14735,7 @@
       <c r="H309" s="13"/>
       <c r="I309" s="13"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="13" t="s">
         <v>697</v>
       </c>
@@ -14780,7 +14779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="13" t="s">
         <v>699</v>
       </c>
@@ -14801,7 +14800,7 @@
       <c r="H311" s="13"/>
       <c r="I311" s="13"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="11" t="s">
         <v>701</v>
       </c>
@@ -14845,7 +14844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="13" t="s">
         <v>703</v>
       </c>
@@ -14866,7 +14865,7 @@
       <c r="H313" s="13"/>
       <c r="I313" s="13"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="13" t="s">
         <v>705</v>
       </c>
@@ -14907,7 +14906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="13" t="s">
         <v>707</v>
       </c>
@@ -14931,7 +14930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="13" t="s">
         <v>710</v>
       </c>
@@ -14975,7 +14974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="13" t="s">
         <v>712</v>
       </c>
@@ -15044,7 +15043,7 @@
       <c r="H318" s="13"/>
       <c r="I318" s="13"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="13" t="s">
         <v>717</v>
       </c>
@@ -15085,7 +15084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="13" t="s">
         <v>719</v>
       </c>
@@ -15106,7 +15105,7 @@
       <c r="H320" s="13"/>
       <c r="I320" s="13"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="13" t="s">
         <v>721</v>
       </c>
@@ -15127,7 +15126,7 @@
       <c r="H321" s="13"/>
       <c r="I321" s="13"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="13" t="s">
         <v>723</v>
       </c>
@@ -15171,7 +15170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="13" t="s">
         <v>725</v>
       </c>
@@ -15195,7 +15194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="13" t="s">
         <v>727</v>
       </c>
@@ -15239,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="13" t="s">
         <v>730</v>
       </c>
@@ -15260,7 +15259,7 @@
       <c r="H325" s="13"/>
       <c r="I325" s="13"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="13" t="s">
         <v>732</v>
       </c>
@@ -15304,7 +15303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
         <v>734</v>
       </c>
@@ -15325,7 +15324,7 @@
       <c r="H327" s="13"/>
       <c r="I327" s="13"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="13" t="s">
         <v>736</v>
       </c>
@@ -15413,7 +15412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="13" t="s">
         <v>740</v>
       </c>
@@ -15454,7 +15453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="13" t="s">
         <v>743</v>
       </c>
@@ -15498,7 +15497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="13" t="s">
         <v>745</v>
       </c>
@@ -15519,7 +15518,7 @@
       <c r="H332" s="13"/>
       <c r="I332" s="13"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="13" t="s">
         <v>747</v>
       </c>
@@ -15540,7 +15539,7 @@
       <c r="H333" s="13"/>
       <c r="I333" s="13"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="13" t="s">
         <v>750</v>
       </c>
@@ -15581,7 +15580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="13" t="s">
         <v>752</v>
       </c>
@@ -15602,7 +15601,7 @@
       <c r="H335" s="13"/>
       <c r="I335" s="13"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="13" t="s">
         <v>754</v>
       </c>
@@ -15646,7 +15645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="13" t="s">
         <v>756</v>
       </c>
@@ -15667,7 +15666,7 @@
       <c r="H337" s="13"/>
       <c r="I337" s="13"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="13" t="s">
         <v>758</v>
       </c>
@@ -15688,7 +15687,7 @@
       <c r="H338" s="13"/>
       <c r="I338" s="13"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="13" t="s">
         <v>760</v>
       </c>
@@ -15732,7 +15731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="13" t="s">
         <v>762</v>
       </c>
@@ -15753,7 +15752,7 @@
       <c r="H340" s="13"/>
       <c r="I340" s="13"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="13" t="s">
         <v>764</v>
       </c>
@@ -15774,7 +15773,7 @@
       <c r="H341" s="13"/>
       <c r="I341" s="13"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="13" t="s">
         <v>766</v>
       </c>
@@ -15818,7 +15817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="13" t="s">
         <v>769</v>
       </c>
@@ -15839,7 +15838,7 @@
       <c r="H343" s="13"/>
       <c r="I343" s="13"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="13" t="s">
         <v>772</v>
       </c>
@@ -15860,7 +15859,7 @@
       <c r="H344" s="13"/>
       <c r="I344" s="13"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="13" t="s">
         <v>774</v>
       </c>
@@ -15881,7 +15880,7 @@
       <c r="H345" s="13"/>
       <c r="I345" s="13"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="13" t="s">
         <v>776</v>
       </c>
@@ -15902,7 +15901,7 @@
       <c r="H346" s="13"/>
       <c r="I346" s="13"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="13" t="s">
         <v>778</v>
       </c>
@@ -15923,7 +15922,7 @@
       <c r="H347" s="13"/>
       <c r="I347" s="13"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="13" t="s">
         <v>780</v>
       </c>
@@ -15967,7 +15966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="13" t="s">
         <v>782</v>
       </c>
@@ -15988,7 +15987,7 @@
       <c r="H349" s="13"/>
       <c r="I349" s="13"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="13" t="s">
         <v>785</v>
       </c>
@@ -16009,7 +16008,7 @@
       <c r="H350" s="13"/>
       <c r="I350" s="13"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="13" t="s">
         <v>787</v>
       </c>
@@ -16030,7 +16029,7 @@
       <c r="H351" s="13"/>
       <c r="I351" s="13"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="13" t="s">
         <v>789</v>
       </c>
@@ -16051,7 +16050,7 @@
       <c r="H352" s="13"/>
       <c r="I352" s="13"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="11" t="s">
         <v>791</v>
       </c>
@@ -16095,7 +16094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="13" t="s">
         <v>793</v>
       </c>
@@ -16119,7 +16118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="11" t="s">
         <v>796</v>
       </c>
@@ -16163,7 +16162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="11" t="s">
         <v>798</v>
       </c>
@@ -16207,7 +16206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="11" t="s">
         <v>800</v>
       </c>
@@ -16228,7 +16227,7 @@
       <c r="H357" s="13"/>
       <c r="I357" s="13"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="11" t="s">
         <v>802</v>
       </c>
@@ -16269,7 +16268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="11" t="s">
         <v>804</v>
       </c>
@@ -16313,7 +16312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="13" t="s">
         <v>807</v>
       </c>
@@ -16334,7 +16333,7 @@
       <c r="H360" s="13"/>
       <c r="I360" s="13"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="13" t="s">
         <v>809</v>
       </c>
@@ -16355,7 +16354,7 @@
       <c r="H361" s="13"/>
       <c r="I361" s="13"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="13" t="s">
         <v>812</v>
       </c>
@@ -16376,7 +16375,7 @@
       <c r="H362" s="13"/>
       <c r="I362" s="13"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="13" t="s">
         <v>814</v>
       </c>
@@ -16397,7 +16396,7 @@
       <c r="H363" s="13"/>
       <c r="I363" s="13"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="13" t="s">
         <v>816</v>
       </c>
@@ -16418,7 +16417,7 @@
       <c r="H364" s="13"/>
       <c r="I364" s="13"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="13" t="s">
         <v>818</v>
       </c>
@@ -16439,7 +16438,7 @@
       <c r="H365" s="13"/>
       <c r="I365" s="13"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="13" t="s">
         <v>820</v>
       </c>
@@ -16460,7 +16459,7 @@
       <c r="H366" s="13"/>
       <c r="I366" s="13"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="13" t="s">
         <v>822</v>
       </c>
@@ -16501,7 +16500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="13" t="s">
         <v>824</v>
       </c>
@@ -16522,7 +16521,7 @@
       <c r="H368" s="13"/>
       <c r="I368" s="13"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="13" t="s">
         <v>826</v>
       </c>
@@ -16543,7 +16542,7 @@
       <c r="H369" s="13"/>
       <c r="I369" s="13"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="13" t="s">
         <v>828</v>
       </c>
@@ -16584,7 +16583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="13" t="s">
         <v>831</v>
       </c>
@@ -16625,7 +16624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="13" t="s">
         <v>833</v>
       </c>
@@ -16646,7 +16645,7 @@
       <c r="H372" s="13"/>
       <c r="I372" s="13"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="13" t="s">
         <v>835</v>
       </c>
@@ -16670,7 +16669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="13" t="s">
         <v>837</v>
       </c>
@@ -16691,7 +16690,7 @@
       <c r="H374" s="13"/>
       <c r="I374" s="13"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="13" t="s">
         <v>839</v>
       </c>
@@ -16712,7 +16711,7 @@
       <c r="H375" s="13"/>
       <c r="I375" s="13"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="13" t="s">
         <v>841</v>
       </c>
@@ -16733,7 +16732,7 @@
       <c r="H376" s="13"/>
       <c r="I376" s="13"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="13" t="s">
         <v>843</v>
       </c>
@@ -16754,7 +16753,7 @@
       <c r="H377" s="13"/>
       <c r="I377" s="13"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="13" t="s">
         <v>845</v>
       </c>
@@ -16798,7 +16797,7 @@
       <c r="H379" s="13"/>
       <c r="I379" s="13"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="11" t="s">
         <v>849</v>
       </c>
@@ -16842,7 +16841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="13" t="s">
         <v>852</v>
       </c>
@@ -16863,7 +16862,7 @@
       <c r="H381" s="13"/>
       <c r="I381" s="13"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="13" t="s">
         <v>854</v>
       </c>
@@ -16907,7 +16906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="13" t="s">
         <v>857</v>
       </c>
@@ -16926,7 +16925,7 @@
       <c r="H383" s="13"/>
       <c r="I383" s="13"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="13" t="s">
         <v>859</v>
       </c>
@@ -16970,7 +16969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="13" t="s">
         <v>861</v>
       </c>
@@ -16989,7 +16988,7 @@
       <c r="H385" s="13"/>
       <c r="I385" s="13"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="16" t="s">
         <v>863</v>
       </c>
@@ -17033,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="16" t="s">
         <v>866</v>
       </c>
@@ -17052,7 +17051,7 @@
       <c r="H387" s="13"/>
       <c r="I387" s="13"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="13" t="s">
         <v>869</v>
       </c>
@@ -17071,7 +17070,7 @@
       <c r="H388" s="13"/>
       <c r="I388" s="13"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="13" t="s">
         <v>872</v>
       </c>
@@ -17115,7 +17114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="13" t="s">
         <v>874</v>
       </c>
@@ -17137,7 +17136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="13" t="s">
         <v>876</v>
       </c>
@@ -17181,7 +17180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="16" t="s">
         <v>878</v>
       </c>
@@ -17202,7 +17201,7 @@
       <c r="H392" s="13"/>
       <c r="I392" s="13"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="13" t="s">
         <v>881</v>
       </c>
@@ -17246,7 +17245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="16" t="s">
         <v>884</v>
       </c>
@@ -17290,7 +17289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="13" t="s">
         <v>887</v>
       </c>
@@ -17309,7 +17308,7 @@
       <c r="H395" s="13"/>
       <c r="I395" s="13"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
         <v>889</v>
       </c>
@@ -17328,7 +17327,7 @@
       <c r="H396" s="13"/>
       <c r="I396" s="13"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="13" t="s">
         <v>891</v>
       </c>
@@ -17372,7 +17371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="13" t="s">
         <v>893</v>
       </c>
@@ -17416,7 +17415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="13" t="s">
         <v>895</v>
       </c>
@@ -17435,7 +17434,7 @@
       <c r="H399" s="13"/>
       <c r="I399" s="13"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="16" t="s">
         <v>897</v>
       </c>
@@ -17454,7 +17453,7 @@
       <c r="H400" s="13"/>
       <c r="I400" s="13"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="13" t="s">
         <v>900</v>
       </c>
@@ -17498,7 +17497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="13" t="s">
         <v>902</v>
       </c>
@@ -17526,7 +17525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="13" t="s">
         <v>904</v>
       </c>
@@ -17570,7 +17569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="13" t="s">
         <v>907</v>
       </c>
@@ -17614,7 +17613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="13" t="s">
         <v>909</v>
       </c>
@@ -17633,7 +17632,7 @@
       <c r="H405" s="13"/>
       <c r="I405" s="13"/>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="13" t="s">
         <v>911</v>
       </c>
@@ -17652,7 +17651,7 @@
       <c r="H406" s="13"/>
       <c r="I406" s="13"/>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="13" t="s">
         <v>914</v>
       </c>
@@ -17696,7 +17695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="11" t="s">
         <v>916</v>
       </c>
@@ -17740,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="13" t="s">
         <v>919</v>
       </c>
@@ -17759,7 +17758,7 @@
       <c r="H409" s="13"/>
       <c r="I409" s="13"/>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="13" t="s">
         <v>921</v>
       </c>
@@ -17803,7 +17802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="13" t="s">
         <v>924</v>
       </c>
@@ -17822,7 +17821,7 @@
       <c r="H411" s="13"/>
       <c r="I411" s="13"/>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="13" t="s">
         <v>927</v>
       </c>
@@ -17866,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="13" t="s">
         <v>929</v>
       </c>
@@ -17885,7 +17884,7 @@
       <c r="H413" s="13"/>
       <c r="I413" s="13"/>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="13" t="s">
         <v>931</v>
       </c>
@@ -17929,7 +17928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="13" t="s">
         <v>933</v>
       </c>
@@ -17948,7 +17947,7 @@
       <c r="H415" s="13"/>
       <c r="I415" s="13"/>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="13" t="s">
         <v>935</v>
       </c>
@@ -17992,7 +17991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="13" t="s">
         <v>938</v>
       </c>
@@ -18011,7 +18010,7 @@
       <c r="H417" s="13"/>
       <c r="I417" s="13"/>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="10" t="s">
         <v>940</v>
       </c>
@@ -18033,7 +18032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="13" t="s">
         <v>942</v>
       </c>
@@ -18077,7 +18076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="13" t="s">
         <v>945</v>
       </c>
@@ -18105,7 +18104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="13" t="s">
         <v>948</v>
       </c>
@@ -18149,7 +18148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="13" t="s">
         <v>950</v>
       </c>
@@ -18193,7 +18192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="13" t="s">
         <v>952</v>
       </c>
@@ -18221,7 +18220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="13" t="s">
         <v>954</v>
       </c>
@@ -18265,7 +18264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="13" t="s">
         <v>956</v>
       </c>
@@ -18284,7 +18283,7 @@
       <c r="H425" s="13"/>
       <c r="I425" s="13"/>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="16" t="s">
         <v>958</v>
       </c>
@@ -18328,7 +18327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="13" t="s">
         <v>961</v>
       </c>
@@ -18356,7 +18355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="13" t="s">
         <v>963</v>
       </c>
@@ -18400,7 +18399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="13" t="s">
         <v>965</v>
       </c>
@@ -18422,7 +18421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="13" t="s">
         <v>967</v>
       </c>
@@ -18466,7 +18465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="16" t="s">
         <v>969</v>
       </c>
@@ -18485,7 +18484,7 @@
       <c r="H431" s="13"/>
       <c r="I431" s="13"/>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="13" t="s">
         <v>971</v>
       </c>
@@ -18504,7 +18503,7 @@
       <c r="H432" s="13"/>
       <c r="I432" s="13"/>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="13" t="s">
         <v>974</v>
       </c>
@@ -18548,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="13" t="s">
         <v>976</v>
       </c>
@@ -18567,7 +18566,7 @@
       <c r="H434" s="13"/>
       <c r="I434" s="13"/>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="13" t="s">
         <v>978</v>
       </c>
@@ -18611,7 +18610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="13" t="s">
         <v>980</v>
       </c>
@@ -18655,7 +18654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="13" t="s">
         <v>982</v>
       </c>
@@ -18674,7 +18673,7 @@
       <c r="H437" s="13"/>
       <c r="I437" s="13"/>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="13" t="s">
         <v>985</v>
       </c>
@@ -18718,7 +18717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="13" t="s">
         <v>988</v>
       </c>
@@ -18740,7 +18739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
         <v>990</v>
       </c>
@@ -18784,7 +18783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="16" t="s">
         <v>993</v>
       </c>
@@ -18828,7 +18827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="13" t="s">
         <v>996</v>
       </c>
@@ -18847,7 +18846,7 @@
       <c r="H442" s="13"/>
       <c r="I442" s="13"/>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="13" t="s">
         <v>999</v>
       </c>
@@ -18891,7 +18890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="13" t="s">
         <v>1001</v>
       </c>
@@ -18910,7 +18909,7 @@
       <c r="H444" s="13"/>
       <c r="I444" s="13"/>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="27" t="s">
         <v>1004</v>
       </c>
@@ -18930,7 +18929,7 @@
       <c r="I445" s="13"/>
       <c r="J445" s="13"/>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="13" t="s">
         <v>1006</v>
       </c>
@@ -18974,7 +18973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
         <v>1008</v>
       </c>
@@ -18993,7 +18992,7 @@
       <c r="H447" s="13"/>
       <c r="I447" s="13"/>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="13" t="s">
         <v>1011</v>
       </c>
@@ -19037,7 +19036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="28" t="s">
         <v>1014</v>
       </c>
@@ -19081,7 +19080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="13" t="s">
         <v>1016</v>
       </c>
@@ -19103,7 +19102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
         <v>1018</v>
       </c>
@@ -19147,7 +19146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="13" t="s">
         <v>1021</v>
       </c>
@@ -19166,7 +19165,7 @@
       <c r="H452" s="13"/>
       <c r="I452" s="13"/>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="13" t="s">
         <v>1024</v>
       </c>
@@ -19210,7 +19209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="13" t="s">
         <v>1026</v>
       </c>
@@ -19229,7 +19228,7 @@
       <c r="H454" s="13"/>
       <c r="I454" s="13"/>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="13" t="s">
         <v>1028</v>
       </c>
@@ -19273,7 +19272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="10" t="s">
         <v>1030</v>
       </c>
@@ -19295,7 +19294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="13" t="s">
         <v>1032</v>
       </c>
@@ -19314,7 +19313,7 @@
       <c r="H457" s="13"/>
       <c r="I457" s="13"/>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="13" t="s">
         <v>1035</v>
       </c>
@@ -19358,7 +19357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="10" t="s">
         <v>1037</v>
       </c>
@@ -19402,7 +19401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="10" t="s">
         <v>1039</v>
       </c>
@@ -19424,7 +19423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="13" t="s">
         <v>1041</v>
       </c>
@@ -19468,7 +19467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
         <v>1044</v>
       </c>
@@ -19512,7 +19511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="16" t="s">
         <v>1046</v>
       </c>
@@ -19556,7 +19555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="13" t="s">
         <v>1048</v>
       </c>
@@ -19644,7 +19643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="13" t="s">
         <v>1053</v>
       </c>
@@ -19688,7 +19687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="13" t="s">
         <v>1056</v>
       </c>
@@ -19707,7 +19706,7 @@
       <c r="H467" s="13"/>
       <c r="I467" s="13"/>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="13" t="s">
         <v>1058</v>
       </c>
@@ -19726,7 +19725,7 @@
       <c r="H468" s="13"/>
       <c r="I468" s="13"/>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="13" t="s">
         <v>1060</v>
       </c>
@@ -19770,7 +19769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
         <v>1062</v>
       </c>
@@ -19789,7 +19788,7 @@
       <c r="H470" s="13"/>
       <c r="I470" s="13"/>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="13" t="s">
         <v>1064</v>
       </c>
@@ -19833,7 +19832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="13" t="s">
         <v>1066</v>
       </c>
@@ -19877,7 +19876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="13" t="s">
         <v>1069</v>
       </c>
@@ -19896,7 +19895,7 @@
       <c r="H473" s="13"/>
       <c r="I473" s="13"/>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="13" t="s">
         <v>1071</v>
       </c>
@@ -19940,7 +19939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="13" t="s">
         <v>1074</v>
       </c>
@@ -19959,7 +19958,7 @@
       <c r="H475" s="13"/>
       <c r="I475" s="13"/>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="13" t="s">
         <v>1076</v>
       </c>
@@ -20003,7 +20002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="13" t="s">
         <v>1078</v>
       </c>
@@ -20025,7 +20024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="13" t="s">
         <v>1081</v>
       </c>
@@ -20069,7 +20068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="13" t="s">
         <v>1084</v>
       </c>
@@ -20094,7 +20093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="13" t="s">
         <v>1086</v>
       </c>
@@ -20138,7 +20137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="13" t="s">
         <v>1088</v>
       </c>
@@ -20157,7 +20156,7 @@
       <c r="H481" s="13"/>
       <c r="I481" s="13"/>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="13" t="s">
         <v>1091</v>
       </c>
@@ -20201,7 +20200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="13" t="s">
         <v>1093</v>
       </c>
@@ -20229,7 +20228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="13" t="s">
         <v>1095</v>
       </c>
@@ -20273,7 +20272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="13" t="s">
         <v>1097</v>
       </c>
@@ -20317,7 +20316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="13" t="s">
         <v>1100</v>
       </c>
@@ -20336,7 +20335,7 @@
       <c r="H486" s="13"/>
       <c r="I486" s="13"/>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="13" t="s">
         <v>1102</v>
       </c>
@@ -20355,7 +20354,7 @@
       <c r="H487" s="13"/>
       <c r="I487" s="13"/>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="13" t="s">
         <v>1105</v>
       </c>
@@ -20374,7 +20373,7 @@
       <c r="H488" s="13"/>
       <c r="I488" s="13"/>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="13" t="s">
         <v>1108</v>
       </c>
@@ -20418,7 +20417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="13" t="s">
         <v>1110</v>
       </c>
@@ -20462,7 +20461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="13" t="s">
         <v>1112</v>
       </c>
@@ -20481,7 +20480,7 @@
       <c r="H491" s="13"/>
       <c r="I491" s="13"/>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="13" t="s">
         <v>1114</v>
       </c>
@@ -20525,7 +20524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="13" t="s">
         <v>1116</v>
       </c>
@@ -20544,7 +20543,7 @@
       <c r="H493" s="13"/>
       <c r="I493" s="13"/>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="13" t="s">
         <v>1118</v>
       </c>
@@ -20580,7 +20579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="13" t="s">
         <v>1120</v>
       </c>
@@ -20599,7 +20598,7 @@
       <c r="H495" s="13"/>
       <c r="I495" s="13"/>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="13" t="s">
         <v>1122</v>
       </c>
@@ -20618,7 +20617,7 @@
       <c r="H496" s="13"/>
       <c r="I496" s="13"/>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="7" t="s">
         <v>1124</v>
       </c>
@@ -20662,7 +20661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="13" t="s">
         <v>1126</v>
       </c>
@@ -20706,7 +20705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="13" t="s">
         <v>1128</v>
       </c>
@@ -20728,7 +20727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="7" t="s">
         <v>1130</v>
       </c>
@@ -20772,7 +20771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="13" t="s">
         <v>1133</v>
       </c>
@@ -20816,7 +20815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="13" t="s">
         <v>1135</v>
       </c>
@@ -20844,7 +20843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="7" t="s">
         <v>1137</v>
       </c>
@@ -20888,7 +20887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="13" t="s">
         <v>1139</v>
       </c>
@@ -20910,7 +20909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="13" t="s">
         <v>1142</v>
       </c>
@@ -20954,7 +20953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="6" t="s">
         <v>1144</v>
       </c>
@@ -20998,7 +20997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="24" t="s">
         <v>1146</v>
       </c>
@@ -21042,7 +21041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
         <v>1148</v>
       </c>
@@ -21061,7 +21060,7 @@
       <c r="H508" s="13"/>
       <c r="I508" s="13"/>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
         <v>1150</v>
       </c>
@@ -21105,7 +21104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="13" t="s">
         <v>1152</v>
       </c>
@@ -21124,7 +21123,7 @@
       <c r="H510" s="13"/>
       <c r="I510" s="13"/>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="10" t="s">
         <v>1155</v>
       </c>
@@ -21146,7 +21145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="13" t="s">
         <v>1157</v>
       </c>
@@ -21190,7 +21189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="13" t="s">
         <v>1159</v>
       </c>
@@ -21209,7 +21208,7 @@
       <c r="H513" s="13"/>
       <c r="I513" s="13"/>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
         <v>1161</v>
       </c>
@@ -21253,7 +21252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="13" t="s">
         <v>1163</v>
       </c>
@@ -21297,7 +21296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="13" t="s">
         <v>1165</v>
       </c>
@@ -21341,7 +21340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="13" t="s">
         <v>1167</v>
       </c>
@@ -21360,7 +21359,7 @@
       <c r="H517" s="13"/>
       <c r="I517" s="13"/>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="13" t="s">
         <v>1169</v>
       </c>
@@ -21404,7 +21403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="13" t="s">
         <v>1171</v>
       </c>
@@ -21423,7 +21422,7 @@
       <c r="H519" s="13"/>
       <c r="I519" s="13"/>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="29" t="s">
         <v>1173</v>
       </c>
@@ -21467,7 +21466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="13" t="s">
         <v>1175</v>
       </c>
@@ -21486,7 +21485,7 @@
       <c r="H521" s="13"/>
       <c r="I521" s="13"/>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="13" t="s">
         <v>1178</v>
       </c>
@@ -21530,7 +21529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="13" t="s">
         <v>1180</v>
       </c>
@@ -21593,7 +21592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="13" t="s">
         <v>1185</v>
       </c>
@@ -21637,7 +21636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
         <v>1187</v>
       </c>
@@ -21681,7 +21680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="13" t="s">
         <v>1190</v>
       </c>
@@ -21700,7 +21699,7 @@
       <c r="H527" s="13"/>
       <c r="I527" s="13"/>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="13" t="s">
         <v>1193</v>
       </c>
@@ -21744,7 +21743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="13" t="s">
         <v>1195</v>
       </c>
@@ -21763,7 +21762,7 @@
       <c r="H529" s="13"/>
       <c r="I529" s="13"/>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="13" t="s">
         <v>1197</v>
       </c>
@@ -21807,7 +21806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="10" t="s">
         <v>1199</v>
       </c>
@@ -21832,7 +21831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="13" t="s">
         <v>1202</v>
       </c>
@@ -21851,7 +21850,7 @@
       <c r="H532" s="13"/>
       <c r="I532" s="13"/>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="13" t="s">
         <v>1204</v>
       </c>
@@ -21895,7 +21894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="13" t="s">
         <v>1206</v>
       </c>
@@ -21914,7 +21913,7 @@
       <c r="H534" s="13"/>
       <c r="I534" s="13"/>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="7" t="s">
         <v>1208</v>
       </c>
@@ -21958,7 +21957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="13" t="s">
         <v>1210</v>
       </c>
@@ -22002,7 +22001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="13" t="s">
         <v>1212</v>
       </c>
@@ -22046,7 +22045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="13" t="s">
         <v>1214</v>
       </c>
@@ -22065,7 +22064,7 @@
       <c r="H538" s="13"/>
       <c r="I538" s="13"/>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="13" t="s">
         <v>1216</v>
       </c>
@@ -22084,7 +22083,7 @@
       <c r="H539" s="13"/>
       <c r="I539" s="13"/>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="13" t="s">
         <v>1218</v>
       </c>
@@ -22128,7 +22127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="13" t="s">
         <v>1220</v>
       </c>
@@ -22172,7 +22171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="13" t="s">
         <v>1222</v>
       </c>
@@ -22191,7 +22190,7 @@
       <c r="H542" s="13"/>
       <c r="I542" s="13"/>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="13" t="s">
         <v>1224</v>
       </c>
@@ -22210,7 +22209,7 @@
       <c r="H543" s="13"/>
       <c r="I543" s="13"/>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="13" t="s">
         <v>1226</v>
       </c>
@@ -22254,7 +22253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="13" t="s">
         <v>1228</v>
       </c>
@@ -22298,7 +22297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="13" t="s">
         <v>1231</v>
       </c>
@@ -22317,7 +22316,7 @@
       <c r="H546" s="13"/>
       <c r="I546" s="13"/>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="13" t="s">
         <v>1233</v>
       </c>
@@ -22361,7 +22360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="13" t="s">
         <v>1235</v>
       </c>
@@ -22380,7 +22379,7 @@
       <c r="H548" s="13"/>
       <c r="I548" s="13"/>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="13" t="s">
         <v>1237</v>
       </c>
@@ -22399,7 +22398,7 @@
       <c r="H549" s="13"/>
       <c r="I549" s="13"/>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="13" t="s">
         <v>1239</v>
       </c>
@@ -22443,7 +22442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="13" t="s">
         <v>1241</v>
       </c>
@@ -22487,7 +22486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="13" t="s">
         <v>1243</v>
       </c>
@@ -22506,7 +22505,7 @@
       <c r="H552" s="13"/>
       <c r="I552" s="13"/>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="13" t="s">
         <v>1245</v>
       </c>
@@ -22525,7 +22524,7 @@
       <c r="H553" s="13"/>
       <c r="I553" s="13"/>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="13" t="s">
         <v>1248</v>
       </c>
@@ -22569,7 +22568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="16" t="s">
         <v>1250</v>
       </c>
@@ -22613,7 +22612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="13" t="s">
         <v>1252</v>
       </c>
@@ -22632,7 +22631,7 @@
       <c r="H556" s="13"/>
       <c r="I556" s="13"/>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="13" t="s">
         <v>1255</v>
       </c>
@@ -22676,7 +22675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="13" t="s">
         <v>1257</v>
       </c>
@@ -22695,7 +22694,7 @@
       <c r="H558" s="13"/>
       <c r="I558" s="13"/>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="13" t="s">
         <v>1259</v>
       </c>
@@ -22739,7 +22738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="13" t="s">
         <v>1261</v>
       </c>
@@ -22761,7 +22760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="13" t="s">
         <v>1263</v>
       </c>
@@ -22805,7 +22804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="13" t="s">
         <v>1265</v>
       </c>
@@ -22824,7 +22823,7 @@
       <c r="H562" s="13"/>
       <c r="I562" s="13"/>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="13" t="s">
         <v>1267</v>
       </c>
@@ -22849,7 +22848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="13" t="s">
         <v>1269</v>
       </c>
@@ -22925,7 +22924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="13" t="s">
         <v>1273</v>
       </c>
@@ -22954,7 +22953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="13" t="s">
         <v>1275</v>
       </c>
@@ -22982,7 +22981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="16" t="s">
         <v>1277</v>
       </c>
@@ -23026,7 +23025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="13" t="s">
         <v>1279</v>
       </c>
@@ -23070,7 +23069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="13" t="s">
         <v>1282</v>
       </c>
@@ -23089,7 +23088,7 @@
       <c r="H570" s="13"/>
       <c r="I570" s="13"/>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="13" t="s">
         <v>1285</v>
       </c>
@@ -23133,7 +23132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="13" t="s">
         <v>1287</v>
       </c>
@@ -23152,7 +23151,7 @@
       <c r="H572" s="13"/>
       <c r="I572" s="13"/>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="13" t="s">
         <v>1289</v>
       </c>
@@ -23196,7 +23195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="13" t="s">
         <v>1291</v>
       </c>
@@ -23215,7 +23214,7 @@
       <c r="H574" s="13"/>
       <c r="I574" s="13"/>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="13" t="s">
         <v>1293</v>
       </c>
@@ -23259,7 +23258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="13" t="s">
         <v>1295</v>
       </c>
@@ -23278,7 +23277,7 @@
       <c r="H576" s="13"/>
       <c r="I576" s="13"/>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="13" t="s">
         <v>1297</v>
       </c>
@@ -23297,7 +23296,7 @@
       <c r="H577" s="13"/>
       <c r="I577" s="13"/>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="13" t="s">
         <v>1299</v>
       </c>
@@ -23316,7 +23315,7 @@
       <c r="H578" s="13"/>
       <c r="I578" s="13"/>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="13" t="s">
         <v>1301</v>
       </c>
@@ -23357,7 +23356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="13" t="s">
         <v>1303</v>
       </c>
@@ -23376,7 +23375,7 @@
       <c r="H580" s="13"/>
       <c r="I580" s="13"/>
     </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="13" t="s">
         <v>1305</v>
       </c>
@@ -23420,7 +23419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="13" t="s">
         <v>1307</v>
       </c>
@@ -23439,7 +23438,7 @@
       <c r="H582" s="13"/>
       <c r="I582" s="13"/>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="13" t="s">
         <v>1309</v>
       </c>
@@ -23480,7 +23479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="13" t="s">
         <v>1311</v>
       </c>
@@ -23524,7 +23523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="13" t="s">
         <v>1313</v>
       </c>
@@ -23543,7 +23542,7 @@
       <c r="H585" s="13"/>
       <c r="I585" s="13"/>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="13" t="s">
         <v>1315</v>
       </c>
@@ -23562,7 +23561,7 @@
       <c r="H586" s="13"/>
       <c r="I586" s="13"/>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="13" t="s">
         <v>1317</v>
       </c>
@@ -23606,7 +23605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="13" t="s">
         <v>1319</v>
       </c>
@@ -23650,7 +23649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="13" t="s">
         <v>1321</v>
       </c>
@@ -23713,7 +23712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="13" t="s">
         <v>1325</v>
       </c>
@@ -23757,7 +23756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="13" t="s">
         <v>1327</v>
       </c>
@@ -23801,7 +23800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="13" t="s">
         <v>1329</v>
       </c>
@@ -23826,7 +23825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="13" t="s">
         <v>1332</v>
       </c>
@@ -23848,7 +23847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
         <v>1334</v>
       </c>
@@ -23892,7 +23891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
         <v>1336</v>
       </c>
@@ -23911,7 +23910,7 @@
       <c r="H596" s="13"/>
       <c r="I596" s="13"/>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="13" t="s">
         <v>1338</v>
       </c>
@@ -23946,7 +23945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="6" t="s">
         <v>1340</v>
       </c>
@@ -23965,7 +23964,7 @@
       <c r="H598" s="13"/>
       <c r="I598" s="13"/>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
         <v>1342</v>
       </c>
@@ -24010,6 +24009,19 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N599">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="1"/>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/01. Preprocessing data/data_CSV/04_ABUS.xlsx
+++ b/01. Preprocessing data/data_CSV/04_ABUS.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Discr" sheetId="1" r:id="rId1"/>
-    <sheet name="ABUSnodleSize" sheetId="2" r:id="rId2"/>
-    <sheet name="ABUSnodleContours" sheetId="3" r:id="rId3"/>
-    <sheet name="ABUSstructure" sheetId="4" r:id="rId4"/>
-    <sheet name="ABUSdiagnosis" sheetId="5" r:id="rId5"/>
+    <sheet name="ABUSisTumor" sheetId="6" r:id="rId2"/>
+    <sheet name="ABUSnodleSize" sheetId="2" r:id="rId3"/>
+    <sheet name="ABUSnodleContours" sheetId="3" r:id="rId4"/>
+    <sheet name="ABUSstructure" sheetId="4" r:id="rId5"/>
+    <sheet name="ABUSdiagnosis" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ABUSdiagnosis!$A$1:$C$608</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ABUSnodleContours!$A$1:$C$603</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ABUSnodleSize!$A$1:$C$611</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ABUSstructure!$A$1:$C$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ABUSdiagnosis!$A$1:$C$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ABUSnodleContours!$A$1:$C$603</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ABUSnodleSize!$A$1:$C$611</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ABUSstructure!$A$1:$C$601</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Discr!$A$1:$H$599</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6054" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7253" uniqueCount="1226">
   <si>
     <t>ID</t>
   </si>
@@ -3702,13 +3703,19 @@
   </si>
   <si>
     <t>id610</t>
+  </si>
+  <si>
+    <t>IDisTumor</t>
+  </si>
+  <si>
+    <t>isTumor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3751,6 +3758,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -3848,7 +3864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3888,11 +3904,63 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -19934,16 +20002,6635 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист6"/>
+  <dimension ref="A1:C599"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
+        <v>619</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" t="s">
+        <v>620</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>622</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>478</v>
+      </c>
+      <c r="B11" t="s">
+        <v>623</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" t="s">
+        <v>624</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" t="s">
+        <v>625</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" t="s">
+        <v>626</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>627</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" t="s">
+        <v>628</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>629</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" t="s">
+        <v>630</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>588</v>
+      </c>
+      <c r="B19" t="s">
+        <v>631</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" t="s">
+        <v>632</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>539</v>
+      </c>
+      <c r="B21" t="s">
+        <v>633</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>634</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>635</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" t="s">
+        <v>636</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
+        <v>637</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" t="s">
+        <v>638</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>639</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>640</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" t="s">
+        <v>641</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>377</v>
+      </c>
+      <c r="B30" t="s">
+        <v>642</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>374</v>
+      </c>
+      <c r="B31" t="s">
+        <v>643</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" t="s">
+        <v>644</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>470</v>
+      </c>
+      <c r="B33" t="s">
+        <v>645</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>499</v>
+      </c>
+      <c r="B34" t="s">
+        <v>646</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B35" t="s">
+        <v>647</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" t="s">
+        <v>648</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>649</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>446</v>
+      </c>
+      <c r="B38" t="s">
+        <v>650</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
+        <v>651</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>440</v>
+      </c>
+      <c r="B40" t="s">
+        <v>652</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" t="s">
+        <v>653</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B42" t="s">
+        <v>654</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>504</v>
+      </c>
+      <c r="B43" t="s">
+        <v>655</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>488</v>
+      </c>
+      <c r="B44" t="s">
+        <v>656</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>568</v>
+      </c>
+      <c r="B45" t="s">
+        <v>657</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>572</v>
+      </c>
+      <c r="B46" t="s">
+        <v>658</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" t="s">
+        <v>659</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>571</v>
+      </c>
+      <c r="B48" t="s">
+        <v>660</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>277</v>
+      </c>
+      <c r="B49" t="s">
+        <v>661</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" t="s">
+        <v>662</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>375</v>
+      </c>
+      <c r="B51" t="s">
+        <v>663</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>452</v>
+      </c>
+      <c r="B52" t="s">
+        <v>664</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53" t="s">
+        <v>665</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>666</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>419</v>
+      </c>
+      <c r="B55" t="s">
+        <v>667</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
+        <v>668</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" t="s">
+        <v>669</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>670</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>362</v>
+      </c>
+      <c r="B59" t="s">
+        <v>671</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>672</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>459</v>
+      </c>
+      <c r="B61" t="s">
+        <v>673</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>269</v>
+      </c>
+      <c r="B62" t="s">
+        <v>674</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>327</v>
+      </c>
+      <c r="B63" t="s">
+        <v>675</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" t="s">
+        <v>676</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" t="s">
+        <v>677</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" t="s">
+        <v>678</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>449</v>
+      </c>
+      <c r="B67" t="s">
+        <v>679</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>680</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>515</v>
+      </c>
+      <c r="B69" t="s">
+        <v>681</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" t="s">
+        <v>682</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" t="s">
+        <v>683</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
+        <v>684</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" t="s">
+        <v>685</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>545</v>
+      </c>
+      <c r="B74" t="s">
+        <v>686</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" t="s">
+        <v>687</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>688</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" t="s">
+        <v>689</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>433</v>
+      </c>
+      <c r="B78" t="s">
+        <v>690</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" t="s">
+        <v>691</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>357</v>
+      </c>
+      <c r="B80" t="s">
+        <v>692</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>295</v>
+      </c>
+      <c r="B81" t="s">
+        <v>693</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>178</v>
+      </c>
+      <c r="B82" t="s">
+        <v>694</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>345</v>
+      </c>
+      <c r="B83" t="s">
+        <v>695</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" t="s">
+        <v>696</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>548</v>
+      </c>
+      <c r="B85" t="s">
+        <v>697</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86" t="s">
+        <v>698</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>559</v>
+      </c>
+      <c r="B87" t="s">
+        <v>699</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" t="s">
+        <v>700</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>531</v>
+      </c>
+      <c r="B89" t="s">
+        <v>701</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90" t="s">
+        <v>702</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>480</v>
+      </c>
+      <c r="B91" t="s">
+        <v>703</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>441</v>
+      </c>
+      <c r="B92" t="s">
+        <v>704</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>337</v>
+      </c>
+      <c r="B93" t="s">
+        <v>705</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" t="s">
+        <v>706</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>570</v>
+      </c>
+      <c r="B95" t="s">
+        <v>707</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>231</v>
+      </c>
+      <c r="B96" t="s">
+        <v>708</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B97" t="s">
+        <v>709</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" t="s">
+        <v>710</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>474</v>
+      </c>
+      <c r="B99" t="s">
+        <v>711</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>404</v>
+      </c>
+      <c r="B100" t="s">
+        <v>712</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" t="s">
+        <v>713</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>151</v>
+      </c>
+      <c r="B102" t="s">
+        <v>714</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" t="s">
+        <v>715</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>587</v>
+      </c>
+      <c r="B104" t="s">
+        <v>716</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" t="s">
+        <v>717</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>392</v>
+      </c>
+      <c r="B106" t="s">
+        <v>718</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>719</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>420</v>
+      </c>
+      <c r="B108" t="s">
+        <v>720</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>66</v>
+      </c>
+      <c r="B109" t="s">
+        <v>721</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>413</v>
+      </c>
+      <c r="B110" t="s">
+        <v>722</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>445</v>
+      </c>
+      <c r="B111" t="s">
+        <v>723</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>421</v>
+      </c>
+      <c r="B112" t="s">
+        <v>724</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>195</v>
+      </c>
+      <c r="B113" t="s">
+        <v>725</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>174</v>
+      </c>
+      <c r="B114" t="s">
+        <v>726</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>411</v>
+      </c>
+      <c r="B115" t="s">
+        <v>727</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116" t="s">
+        <v>728</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" t="s">
+        <v>729</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s">
+        <v>730</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>287</v>
+      </c>
+      <c r="B119" t="s">
+        <v>731</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>447</v>
+      </c>
+      <c r="B120" t="s">
+        <v>732</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>505</v>
+      </c>
+      <c r="B121" t="s">
+        <v>733</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>584</v>
+      </c>
+      <c r="B122" t="s">
+        <v>734</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>581</v>
+      </c>
+      <c r="B123" t="s">
+        <v>735</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>310</v>
+      </c>
+      <c r="B124" t="s">
+        <v>736</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>590</v>
+      </c>
+      <c r="B125" t="s">
+        <v>737</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>534</v>
+      </c>
+      <c r="B126" t="s">
+        <v>738</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>739</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>165</v>
+      </c>
+      <c r="B128" t="s">
+        <v>740</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" t="s">
+        <v>741</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>210</v>
+      </c>
+      <c r="B130" t="s">
+        <v>742</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>486</v>
+      </c>
+      <c r="B131" t="s">
+        <v>743</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>300</v>
+      </c>
+      <c r="B132" t="s">
+        <v>744</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>481</v>
+      </c>
+      <c r="B133" t="s">
+        <v>745</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>119</v>
+      </c>
+      <c r="B134" t="s">
+        <v>746</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>264</v>
+      </c>
+      <c r="B135" t="s">
+        <v>747</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>340</v>
+      </c>
+      <c r="B136" t="s">
+        <v>748</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>576</v>
+      </c>
+      <c r="B137" t="s">
+        <v>749</v>
+      </c>
+      <c r="C137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>406</v>
+      </c>
+      <c r="B138" t="s">
+        <v>750</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>355</v>
+      </c>
+      <c r="B139" t="s">
+        <v>751</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>429</v>
+      </c>
+      <c r="B140" t="s">
+        <v>752</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>594</v>
+      </c>
+      <c r="B141" t="s">
+        <v>753</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s">
+        <v>754</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" t="s">
+        <v>755</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>402</v>
+      </c>
+      <c r="B144" t="s">
+        <v>756</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+      <c r="B145" t="s">
+        <v>757</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>215</v>
+      </c>
+      <c r="B146" t="s">
+        <v>758</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147" t="s">
+        <v>759</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>438</v>
+      </c>
+      <c r="B148" t="s">
+        <v>760</v>
+      </c>
+      <c r="C148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>761</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>235</v>
+      </c>
+      <c r="B150" t="s">
+        <v>762</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>431</v>
+      </c>
+      <c r="B151" t="s">
+        <v>763</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>276</v>
+      </c>
+      <c r="B152" t="s">
+        <v>764</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>236</v>
+      </c>
+      <c r="B153" t="s">
+        <v>765</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>110</v>
+      </c>
+      <c r="B154" t="s">
+        <v>766</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>596</v>
+      </c>
+      <c r="B155" t="s">
+        <v>767</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B156" t="s">
+        <v>768</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>270</v>
+      </c>
+      <c r="B157" t="s">
+        <v>769</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s">
+        <v>770</v>
+      </c>
+      <c r="C158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>322</v>
+      </c>
+      <c r="B159" t="s">
+        <v>771</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>508</v>
+      </c>
+      <c r="B160" t="s">
+        <v>772</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>511</v>
+      </c>
+      <c r="B161" t="s">
+        <v>773</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>214</v>
+      </c>
+      <c r="B162" t="s">
+        <v>774</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>335</v>
+      </c>
+      <c r="B163" t="s">
+        <v>775</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>289</v>
+      </c>
+      <c r="B164" t="s">
+        <v>776</v>
+      </c>
+      <c r="C164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>147</v>
+      </c>
+      <c r="B165" t="s">
+        <v>777</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>347</v>
+      </c>
+      <c r="B166" t="s">
+        <v>778</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>155</v>
+      </c>
+      <c r="B167" t="s">
+        <v>779</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>558</v>
+      </c>
+      <c r="B168" t="s">
+        <v>780</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>125</v>
+      </c>
+      <c r="B169" t="s">
+        <v>781</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" t="s">
+        <v>782</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>348</v>
+      </c>
+      <c r="B171" t="s">
+        <v>783</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>547</v>
+      </c>
+      <c r="B172" t="s">
+        <v>784</v>
+      </c>
+      <c r="C172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>167</v>
+      </c>
+      <c r="B173" t="s">
+        <v>785</v>
+      </c>
+      <c r="C173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>117</v>
+      </c>
+      <c r="B174" t="s">
+        <v>786</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>102</v>
+      </c>
+      <c r="B175" t="s">
+        <v>787</v>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>434</v>
+      </c>
+      <c r="B176" t="s">
+        <v>788</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>230</v>
+      </c>
+      <c r="B177" t="s">
+        <v>789</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>27</v>
+      </c>
+      <c r="B178" t="s">
+        <v>790</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>192</v>
+      </c>
+      <c r="B179" t="s">
+        <v>791</v>
+      </c>
+      <c r="C179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>562</v>
+      </c>
+      <c r="B180" t="s">
+        <v>792</v>
+      </c>
+      <c r="C180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>451</v>
+      </c>
+      <c r="B181" t="s">
+        <v>793</v>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" t="s">
+        <v>794</v>
+      </c>
+      <c r="C182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>5</v>
+      </c>
+      <c r="B183" t="s">
+        <v>795</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>346</v>
+      </c>
+      <c r="B184" t="s">
+        <v>796</v>
+      </c>
+      <c r="C184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>257</v>
+      </c>
+      <c r="B185" t="s">
+        <v>797</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>373</v>
+      </c>
+      <c r="B186" t="s">
+        <v>798</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>98</v>
+      </c>
+      <c r="B187" t="s">
+        <v>799</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>506</v>
+      </c>
+      <c r="B188" t="s">
+        <v>800</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" t="s">
+        <v>801</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>273</v>
+      </c>
+      <c r="B190" t="s">
+        <v>802</v>
+      </c>
+      <c r="C190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>468</v>
+      </c>
+      <c r="B191" t="s">
+        <v>803</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>204</v>
+      </c>
+      <c r="B192" t="s">
+        <v>804</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>100</v>
+      </c>
+      <c r="B193" t="s">
+        <v>805</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" t="s">
+        <v>806</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>361</v>
+      </c>
+      <c r="B195" t="s">
+        <v>807</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>252</v>
+      </c>
+      <c r="B196" t="s">
+        <v>808</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>108</v>
+      </c>
+      <c r="B197" t="s">
+        <v>809</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>500</v>
+      </c>
+      <c r="B198" t="s">
+        <v>810</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>354</v>
+      </c>
+      <c r="B199" t="s">
+        <v>811</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>456</v>
+      </c>
+      <c r="B200" t="s">
+        <v>812</v>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>417</v>
+      </c>
+      <c r="B201" t="s">
+        <v>813</v>
+      </c>
+      <c r="C201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>308</v>
+      </c>
+      <c r="B202" t="s">
+        <v>814</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>563</v>
+      </c>
+      <c r="B203" t="s">
+        <v>815</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>244</v>
+      </c>
+      <c r="B204" t="s">
+        <v>816</v>
+      </c>
+      <c r="C204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>561</v>
+      </c>
+      <c r="B205" t="s">
+        <v>817</v>
+      </c>
+      <c r="C205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>50</v>
+      </c>
+      <c r="B206" t="s">
+        <v>818</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>385</v>
+      </c>
+      <c r="B207" t="s">
+        <v>819</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>442</v>
+      </c>
+      <c r="B208" t="s">
+        <v>820</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>49</v>
+      </c>
+      <c r="B209" t="s">
+        <v>821</v>
+      </c>
+      <c r="C209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>557</v>
+      </c>
+      <c r="B210" t="s">
+        <v>822</v>
+      </c>
+      <c r="C210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>255</v>
+      </c>
+      <c r="B211" t="s">
+        <v>823</v>
+      </c>
+      <c r="C211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>343</v>
+      </c>
+      <c r="B212" t="s">
+        <v>824</v>
+      </c>
+      <c r="C212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>207</v>
+      </c>
+      <c r="B213" t="s">
+        <v>825</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>62</v>
+      </c>
+      <c r="B214" t="s">
+        <v>826</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>201</v>
+      </c>
+      <c r="B215" t="s">
+        <v>827</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>828</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" t="s">
+        <v>829</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" t="s">
+        <v>830</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>543</v>
+      </c>
+      <c r="B219" t="s">
+        <v>831</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>80</v>
+      </c>
+      <c r="B220" t="s">
+        <v>832</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>471</v>
+      </c>
+      <c r="B221" t="s">
+        <v>833</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222" t="s">
+        <v>834</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>104</v>
+      </c>
+      <c r="B223" t="s">
+        <v>835</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>23</v>
+      </c>
+      <c r="B224" t="s">
+        <v>836</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>55</v>
+      </c>
+      <c r="B225" t="s">
+        <v>837</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" t="s">
+        <v>838</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>153</v>
+      </c>
+      <c r="B227" t="s">
+        <v>839</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>490</v>
+      </c>
+      <c r="B228" t="s">
+        <v>840</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>592</v>
+      </c>
+      <c r="B229" t="s">
+        <v>841</v>
+      </c>
+      <c r="C229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>383</v>
+      </c>
+      <c r="B230" t="s">
+        <v>842</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>494</v>
+      </c>
+      <c r="B231" t="s">
+        <v>843</v>
+      </c>
+      <c r="C231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>514</v>
+      </c>
+      <c r="B232" t="s">
+        <v>844</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>566</v>
+      </c>
+      <c r="B233" t="s">
+        <v>845</v>
+      </c>
+      <c r="C233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>579</v>
+      </c>
+      <c r="B234" t="s">
+        <v>846</v>
+      </c>
+      <c r="C234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>328</v>
+      </c>
+      <c r="B235" t="s">
+        <v>847</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>393</v>
+      </c>
+      <c r="B236" t="s">
+        <v>848</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>266</v>
+      </c>
+      <c r="B237" t="s">
+        <v>849</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>388</v>
+      </c>
+      <c r="B238" t="s">
+        <v>850</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>227</v>
+      </c>
+      <c r="B239" t="s">
+        <v>851</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>457</v>
+      </c>
+      <c r="B240" t="s">
+        <v>852</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>95</v>
+      </c>
+      <c r="B241" t="s">
+        <v>853</v>
+      </c>
+      <c r="C241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>61</v>
+      </c>
+      <c r="B242" t="s">
+        <v>854</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>582</v>
+      </c>
+      <c r="B243" t="s">
+        <v>855</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>503</v>
+      </c>
+      <c r="B244" t="s">
+        <v>856</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>426</v>
+      </c>
+      <c r="B245" t="s">
+        <v>857</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>65</v>
+      </c>
+      <c r="B246" t="s">
+        <v>858</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>141</v>
+      </c>
+      <c r="B247" t="s">
+        <v>859</v>
+      </c>
+      <c r="C247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>476</v>
+      </c>
+      <c r="B248" t="s">
+        <v>860</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>64</v>
+      </c>
+      <c r="B249" t="s">
+        <v>861</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>444</v>
+      </c>
+      <c r="B250" t="s">
+        <v>862</v>
+      </c>
+      <c r="C250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>583</v>
+      </c>
+      <c r="B251" t="s">
+        <v>863</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>569</v>
+      </c>
+      <c r="B252" t="s">
+        <v>864</v>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>483</v>
+      </c>
+      <c r="B253" t="s">
+        <v>865</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>475</v>
+      </c>
+      <c r="B254" t="s">
+        <v>866</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>220</v>
+      </c>
+      <c r="B255" t="s">
+        <v>867</v>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>473</v>
+      </c>
+      <c r="B256" t="s">
+        <v>868</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>191</v>
+      </c>
+      <c r="B257" t="s">
+        <v>869</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>439</v>
+      </c>
+      <c r="B258" t="s">
+        <v>870</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>293</v>
+      </c>
+      <c r="B259" t="s">
+        <v>871</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>465</v>
+      </c>
+      <c r="B260" t="s">
+        <v>872</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>546</v>
+      </c>
+      <c r="B261" t="s">
+        <v>873</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>211</v>
+      </c>
+      <c r="B262" t="s">
+        <v>874</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>233</v>
+      </c>
+      <c r="B263" t="s">
+        <v>875</v>
+      </c>
+      <c r="C263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" t="s">
+        <v>876</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>538</v>
+      </c>
+      <c r="B265" t="s">
+        <v>877</v>
+      </c>
+      <c r="C265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>407</v>
+      </c>
+      <c r="B266" t="s">
+        <v>878</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>92</v>
+      </c>
+      <c r="B267" t="s">
+        <v>879</v>
+      </c>
+      <c r="C267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>389</v>
+      </c>
+      <c r="B268" t="s">
+        <v>880</v>
+      </c>
+      <c r="C268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>520</v>
+      </c>
+      <c r="B269" t="s">
+        <v>881</v>
+      </c>
+      <c r="C269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>418</v>
+      </c>
+      <c r="B270" t="s">
+        <v>882</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>319</v>
+      </c>
+      <c r="B271" t="s">
+        <v>883</v>
+      </c>
+      <c r="C271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>556</v>
+      </c>
+      <c r="B272" t="s">
+        <v>884</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>301</v>
+      </c>
+      <c r="B273" t="s">
+        <v>885</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>284</v>
+      </c>
+      <c r="B274" t="s">
+        <v>886</v>
+      </c>
+      <c r="C274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>46</v>
+      </c>
+      <c r="B275" t="s">
+        <v>887</v>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>512</v>
+      </c>
+      <c r="B276" t="s">
+        <v>888</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>331</v>
+      </c>
+      <c r="B277" t="s">
+        <v>889</v>
+      </c>
+      <c r="C277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>507</v>
+      </c>
+      <c r="B278" t="s">
+        <v>890</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>115</v>
+      </c>
+      <c r="B279" t="s">
+        <v>891</v>
+      </c>
+      <c r="C279">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>250</v>
+      </c>
+      <c r="B280" t="s">
+        <v>892</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>454</v>
+      </c>
+      <c r="B281" t="s">
+        <v>893</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>34</v>
+      </c>
+      <c r="B282" t="s">
+        <v>894</v>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>297</v>
+      </c>
+      <c r="B283" t="s">
+        <v>895</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>261</v>
+      </c>
+      <c r="B284" t="s">
+        <v>896</v>
+      </c>
+      <c r="C284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>542</v>
+      </c>
+      <c r="B285" t="s">
+        <v>897</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>72</v>
+      </c>
+      <c r="B286" t="s">
+        <v>898</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>541</v>
+      </c>
+      <c r="B287" t="s">
+        <v>899</v>
+      </c>
+      <c r="C287">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>93</v>
+      </c>
+      <c r="B288" t="s">
+        <v>900</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>196</v>
+      </c>
+      <c r="B289" t="s">
+        <v>901</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>580</v>
+      </c>
+      <c r="B290" t="s">
+        <v>902</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>321</v>
+      </c>
+      <c r="B291" t="s">
+        <v>903</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>356</v>
+      </c>
+      <c r="B292" t="s">
+        <v>904</v>
+      </c>
+      <c r="C292">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>405</v>
+      </c>
+      <c r="B293" t="s">
+        <v>905</v>
+      </c>
+      <c r="C293">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>326</v>
+      </c>
+      <c r="B294" t="s">
+        <v>906</v>
+      </c>
+      <c r="C294">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>386</v>
+      </c>
+      <c r="B295" t="s">
+        <v>907</v>
+      </c>
+      <c r="C295">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>482</v>
+      </c>
+      <c r="B296" t="s">
+        <v>908</v>
+      </c>
+      <c r="C296">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>286</v>
+      </c>
+      <c r="B297" t="s">
+        <v>909</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>279</v>
+      </c>
+      <c r="B298" t="s">
+        <v>910</v>
+      </c>
+      <c r="C298">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>466</v>
+      </c>
+      <c r="B299" t="s">
+        <v>911</v>
+      </c>
+      <c r="C299">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>305</v>
+      </c>
+      <c r="B300" t="s">
+        <v>912</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>577</v>
+      </c>
+      <c r="B301" t="s">
+        <v>913</v>
+      </c>
+      <c r="C301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>435</v>
+      </c>
+      <c r="B302" t="s">
+        <v>914</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>564</v>
+      </c>
+      <c r="B303" t="s">
+        <v>915</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>290</v>
+      </c>
+      <c r="B304" t="s">
+        <v>916</v>
+      </c>
+      <c r="C304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>159</v>
+      </c>
+      <c r="B305" t="s">
+        <v>917</v>
+      </c>
+      <c r="C305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>4</v>
+      </c>
+      <c r="B306" t="s">
+        <v>918</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>555</v>
+      </c>
+      <c r="B307" t="s">
+        <v>919</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>437</v>
+      </c>
+      <c r="B308" t="s">
+        <v>920</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>262</v>
+      </c>
+      <c r="B309" t="s">
+        <v>921</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>113</v>
+      </c>
+      <c r="B310" t="s">
+        <v>922</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>423</v>
+      </c>
+      <c r="B311" t="s">
+        <v>923</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>218</v>
+      </c>
+      <c r="B312" t="s">
+        <v>924</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>26</v>
+      </c>
+      <c r="B313" t="s">
+        <v>925</v>
+      </c>
+      <c r="C313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>260</v>
+      </c>
+      <c r="B314" t="s">
+        <v>926</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>123</v>
+      </c>
+      <c r="B315" t="s">
+        <v>927</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>472</v>
+      </c>
+      <c r="B316" t="s">
+        <v>928</v>
+      </c>
+      <c r="C316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>242</v>
+      </c>
+      <c r="B317" t="s">
+        <v>929</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>424</v>
+      </c>
+      <c r="B318" t="s">
+        <v>930</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>152</v>
+      </c>
+      <c r="B319" t="s">
+        <v>931</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>316</v>
+      </c>
+      <c r="B320" t="s">
+        <v>932</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>169</v>
+      </c>
+      <c r="B321" t="s">
+        <v>933</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>589</v>
+      </c>
+      <c r="B322" t="s">
+        <v>934</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>57</v>
+      </c>
+      <c r="B323" t="s">
+        <v>935</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>131</v>
+      </c>
+      <c r="B324" t="s">
+        <v>936</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>455</v>
+      </c>
+      <c r="B325" t="s">
+        <v>937</v>
+      </c>
+      <c r="C325">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>135</v>
+      </c>
+      <c r="B326" t="s">
+        <v>938</v>
+      </c>
+      <c r="C326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>510</v>
+      </c>
+      <c r="B327" t="s">
+        <v>939</v>
+      </c>
+      <c r="C327">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>10</v>
+      </c>
+      <c r="B328" t="s">
+        <v>940</v>
+      </c>
+      <c r="C328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>68</v>
+      </c>
+      <c r="B329" t="s">
+        <v>941</v>
+      </c>
+      <c r="C329">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>158</v>
+      </c>
+      <c r="B330" t="s">
+        <v>942</v>
+      </c>
+      <c r="C330">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>551</v>
+      </c>
+      <c r="B331" t="s">
+        <v>943</v>
+      </c>
+      <c r="C331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>519</v>
+      </c>
+      <c r="B332" t="s">
+        <v>944</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>492</v>
+      </c>
+      <c r="B333" t="s">
+        <v>945</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>58</v>
+      </c>
+      <c r="B334" t="s">
+        <v>946</v>
+      </c>
+      <c r="C334">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>28</v>
+      </c>
+      <c r="B335" t="s">
+        <v>947</v>
+      </c>
+      <c r="C335">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>281</v>
+      </c>
+      <c r="B336" t="s">
+        <v>948</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>552</v>
+      </c>
+      <c r="B337" t="s">
+        <v>949</v>
+      </c>
+      <c r="C337">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>265</v>
+      </c>
+      <c r="B338" t="s">
+        <v>950</v>
+      </c>
+      <c r="C338">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>412</v>
+      </c>
+      <c r="B339" t="s">
+        <v>951</v>
+      </c>
+      <c r="C339">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>59</v>
+      </c>
+      <c r="B340" t="s">
+        <v>952</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>73</v>
+      </c>
+      <c r="B341" t="s">
+        <v>953</v>
+      </c>
+      <c r="C341">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>370</v>
+      </c>
+      <c r="B342" t="s">
+        <v>954</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>529</v>
+      </c>
+      <c r="B343" t="s">
+        <v>955</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>432</v>
+      </c>
+      <c r="B344" t="s">
+        <v>956</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>111</v>
+      </c>
+      <c r="B345" t="s">
+        <v>957</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>112</v>
+      </c>
+      <c r="B346" t="s">
+        <v>958</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>97</v>
+      </c>
+      <c r="B347" t="s">
+        <v>959</v>
+      </c>
+      <c r="C347">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>528</v>
+      </c>
+      <c r="B348" t="s">
+        <v>960</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>469</v>
+      </c>
+      <c r="B349" t="s">
+        <v>961</v>
+      </c>
+      <c r="C349">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>334</v>
+      </c>
+      <c r="B350" t="s">
+        <v>962</v>
+      </c>
+      <c r="C350">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>185</v>
+      </c>
+      <c r="B351" t="s">
+        <v>963</v>
+      </c>
+      <c r="C351">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>333</v>
+      </c>
+      <c r="B352" t="s">
+        <v>964</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>221</v>
+      </c>
+      <c r="B353" t="s">
+        <v>965</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" t="s">
+        <v>966</v>
+      </c>
+      <c r="C354">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>526</v>
+      </c>
+      <c r="B355" t="s">
+        <v>967</v>
+      </c>
+      <c r="C355">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>208</v>
+      </c>
+      <c r="B356" t="s">
+        <v>968</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>535</v>
+      </c>
+      <c r="B357" t="s">
+        <v>969</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>458</v>
+      </c>
+      <c r="B358" t="s">
+        <v>970</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>69</v>
+      </c>
+      <c r="B359" t="s">
+        <v>971</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>368</v>
+      </c>
+      <c r="B360" t="s">
+        <v>972</v>
+      </c>
+      <c r="C360">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>497</v>
+      </c>
+      <c r="B361" t="s">
+        <v>973</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>517</v>
+      </c>
+      <c r="B362" t="s">
+        <v>974</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>323</v>
+      </c>
+      <c r="B363" t="s">
+        <v>975</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>150</v>
+      </c>
+      <c r="B364" t="s">
+        <v>976</v>
+      </c>
+      <c r="C364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>554</v>
+      </c>
+      <c r="B365" t="s">
+        <v>977</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>518</v>
+      </c>
+      <c r="B366" t="s">
+        <v>978</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>485</v>
+      </c>
+      <c r="B367" t="s">
+        <v>979</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>550</v>
+      </c>
+      <c r="B368" t="s">
+        <v>980</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>352</v>
+      </c>
+      <c r="B369" t="s">
+        <v>981</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>94</v>
+      </c>
+      <c r="B370" t="s">
+        <v>982</v>
+      </c>
+      <c r="C370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>314</v>
+      </c>
+      <c r="B371" t="s">
+        <v>983</v>
+      </c>
+      <c r="C371">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>198</v>
+      </c>
+      <c r="B372" t="s">
+        <v>984</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>313</v>
+      </c>
+      <c r="B373" t="s">
+        <v>985</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>349</v>
+      </c>
+      <c r="B374" t="s">
+        <v>986</v>
+      </c>
+      <c r="C374">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>45</v>
+      </c>
+      <c r="B375" t="s">
+        <v>987</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>524</v>
+      </c>
+      <c r="B376" t="s">
+        <v>988</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>422</v>
+      </c>
+      <c r="B377" t="s">
+        <v>989</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>103</v>
+      </c>
+      <c r="B378" t="s">
+        <v>990</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>360</v>
+      </c>
+      <c r="B379" t="s">
+        <v>991</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>128</v>
+      </c>
+      <c r="B380" t="s">
+        <v>992</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>182</v>
+      </c>
+      <c r="B381" t="s">
+        <v>993</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>67</v>
+      </c>
+      <c r="B382" t="s">
+        <v>994</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>516</v>
+      </c>
+      <c r="B383" t="s">
+        <v>995</v>
+      </c>
+      <c r="C383">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>317</v>
+      </c>
+      <c r="B384" t="s">
+        <v>996</v>
+      </c>
+      <c r="C384">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>591</v>
+      </c>
+      <c r="B385" t="s">
+        <v>997</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>14</v>
+      </c>
+      <c r="B386" t="s">
+        <v>998</v>
+      </c>
+      <c r="C386">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>32</v>
+      </c>
+      <c r="B387" t="s">
+        <v>999</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>222</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>234</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>479</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>38</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>372</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C392">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>462</v>
+      </c>
+      <c r="B393" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>54</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C394">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>146</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>292</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C396">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>189</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C397">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>523</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>124</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>140</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>390</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>463</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>409</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>31</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>575</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>380</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C406">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>585</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C407">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>173</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C408">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>63</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C409">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>216</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C410">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>311</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>186</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>137</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>83</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>384</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C415">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>341</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>578</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>365</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C418">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>549</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>203</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>586</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>527</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>565</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>41</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>197</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C425">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>324</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C426">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>364</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C427">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>595</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C428">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>403</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>161</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>358</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>171</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>241</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C433">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>1</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>484</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>396</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>202</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>232</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C438">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>139</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C439">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>156</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C440">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>251</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>56</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C442">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>291</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>43</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>116</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>7</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C446">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>544</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>329</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>76</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C449">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>39</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>160</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>315</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>350</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C453">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>268</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>164</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>306</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C456">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>109</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>501</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C458">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>84</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>13</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C460">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>399</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C461">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>247</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>2</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>298</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C464">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>118</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>18</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>172</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>493</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>280</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C469">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>598</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>21</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C471">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>177</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>248</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>496</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>487</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C475">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>20</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>154</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C477">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>513</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>19</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>22</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C480">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>342</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C481">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>35</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>205</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>33</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>249</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C485">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>464</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>338</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>142</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>237</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C489">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>330</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>522</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C491">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>42</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C492">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>371</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C493">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>369</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>379</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>376</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C496">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>339</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C497">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>213</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C498">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>285</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>212</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C500">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>303</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C501">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>240</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>209</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C503">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>461</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>238</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>60</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C506">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>533</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C507">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>193</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>144</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>132</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>138</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>187</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C512">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>162</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C513">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>91</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C514">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>79</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C515">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>87</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>136</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>127</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>114</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>126</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C520">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>106</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>96</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>398</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C523">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>78</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>53</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>105</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>88</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>89</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>90</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>443</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C530">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>397</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>81</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>85</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C533">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>70</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>86</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C535">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>381</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>71</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C537">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>51</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>394</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C539">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>47</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C540">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>44</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>382</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C542">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>387</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C543">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>414</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C544">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>400</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>401</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C546">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>540</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>425</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>430</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C549">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>408</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C550">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>410</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C551">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>416</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C552">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>428</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C553">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>450</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>453</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C555">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>597</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C556">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>467</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C557">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>460</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>593</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C559">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>574</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>553</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>530</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C562">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>509</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C563">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>560</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>536</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>537</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C566">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>521</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>498</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C568">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>489</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>495</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C570">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>502</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>259</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C572">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>143</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C573">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>133</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C574">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>309</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>312</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C576">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>395</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C577">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>190</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C578">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>296</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C579">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>294</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C580">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>245</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>148</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C582">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>283</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>363</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C584">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>77</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>491</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>299</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C587">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>243</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C588">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>206</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>253</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C590">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>263</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C591">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>573</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C592">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>272</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>223</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C594">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>332</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C595">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>99</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C596">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>24</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C597">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>183</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C598">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>359</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C599">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1 A600:A1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1 B600:B1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A599">
+    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
   <dimension ref="A1:C611"/>
@@ -26696,7 +33383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист3"/>
   <dimension ref="A1:C603"/>
@@ -33354,7 +40041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист4"/>
   <dimension ref="A1:C601"/>
@@ -39990,7 +46677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист5"/>
   <dimension ref="A1:C608"/>
